--- a/zy72236/samples/sample_batch_1.xlsx
+++ b/zy72236/samples/sample_batch_1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="39">
   <si>
     <t>基金代码</t>
   </si>
@@ -70,9 +70,6 @@
     <t>000003</t>
   </si>
   <si>
-    <t>000004</t>
-  </si>
-  <si>
     <t>华夏成长混合</t>
   </si>
   <si>
@@ -82,9 +79,6 @@
     <t>嘉实沪深300ETF</t>
   </si>
   <si>
-    <t>招商中证白酒指数</t>
-  </si>
-  <si>
     <t>C00001</t>
   </si>
   <si>
@@ -94,9 +88,6 @@
     <t>C00003</t>
   </si>
   <si>
-    <t>C00004</t>
-  </si>
-  <si>
     <t>张三</t>
   </si>
   <si>
@@ -106,9 +97,6 @@
     <t>王五</t>
   </si>
   <si>
-    <t>赵六</t>
-  </si>
-  <si>
     <t>李明</t>
   </si>
   <si>
@@ -136,9 +124,6 @@
     <t>liu yang</t>
   </si>
   <si>
-    <t>陈静</t>
-  </si>
-  <si>
     <t>2024-01-02</t>
   </si>
   <si>
@@ -146,9 +131,6 @@
   </si>
   <si>
     <t>2024-01-01</t>
-  </si>
-  <si>
-    <t>2024-01-04</t>
   </si>
 </sst>
 </file>
@@ -506,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -561,28 +543,28 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
         <v>27</v>
       </c>
-      <c r="E2" t="s">
-        <v>31</v>
-      </c>
       <c r="F2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" t="s">
         <v>37</v>
-      </c>
-      <c r="H2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I2" t="s">
-        <v>42</v>
       </c>
       <c r="J2">
         <v>100000</v>
@@ -608,28 +590,28 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
         <v>28</v>
       </c>
-      <c r="E3" t="s">
-        <v>32</v>
-      </c>
       <c r="F3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="J3">
         <v>250000</v>
@@ -655,28 +637,28 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
         <v>27</v>
       </c>
-      <c r="E4" t="s">
-        <v>31</v>
-      </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" t="s">
         <v>37</v>
-      </c>
-      <c r="H4" t="s">
-        <v>41</v>
-      </c>
-      <c r="I4" t="s">
-        <v>42</v>
       </c>
       <c r="J4">
         <v>100000</v>
@@ -702,28 +684,28 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
         <v>29</v>
       </c>
-      <c r="E5" t="s">
-        <v>33</v>
-      </c>
       <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
         <v>36</v>
       </c>
-      <c r="G5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" t="s">
-        <v>41</v>
-      </c>
       <c r="I5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="J5">
         <v>500000</v>
@@ -742,53 +724,6 @@
       </c>
       <c r="O5">
         <v>450</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J6">
-        <v>80000</v>
-      </c>
-      <c r="K6">
-        <v>0.005</v>
-      </c>
-      <c r="L6">
-        <v>400</v>
-      </c>
-      <c r="M6">
-        <v>120</v>
-      </c>
-      <c r="N6">
-        <v>0.8</v>
-      </c>
-      <c r="O6">
-        <v>96</v>
       </c>
     </row>
   </sheetData>
